--- a/STEP2_ML/Step9_Classical_vs_ML_Comparison.xlsx
+++ b/STEP2_ML/Step9_Classical_vs_ML_Comparison.xlsx
@@ -489,7 +489,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-26 17:08:54</t>
+          <t>2026-10-03 14:57:19</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ML XGBoost achieves 26.38% RMSE reduction over 3rd-order RSM on Vch; Point 71 negative volume (-0.018760) is documented as a known boundary limitation without silent clipping</t>
+          <t>ML XGBoost achieves 19.08% RMSE reduction over 3rd-order RSM on Vch; Point 71 negative volume (0.004437) is documented as a known boundary limitation without silent clipping</t>
         </is>
       </c>
     </row>
@@ -734,38 +734,38 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ExtraTrees (ET_n200_dNone_l1)</t>
+          <t>ExtraTrees (ET_n200_d4_l1)</t>
         </is>
       </c>
       <c r="J2" t="n">
         <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9750992015798391</v>
+        <v>0.9294434588367384</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0332934149654518</v>
+        <v>0.06040846827140765</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9946881263113648</v>
+        <v>0.9799575738731855</v>
       </c>
       <c r="N2" t="n">
-        <v>0.02399813421086183</v>
+        <v>0.04661532901987964</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01564215697529447</v>
+        <v>0.03458174477187558</v>
       </c>
       <c r="P2" t="n">
-        <v>6.997620651245877</v>
+        <v>18.828440260799</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.01583882677059985</v>
+        <v>-0.03845602157961766</v>
       </c>
       <c r="S2" t="n">
-        <v>-194.1197446788608</v>
+        <v>-471.3147759313126</v>
       </c>
       <c r="T2" t="n">
         <v>5.882352941176478</v>
@@ -870,38 +870,38 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>XGBoost (XGB_n200_d2_lr0.05)</t>
+          <t>RandomForest (RF_n200_dNone_l1)</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>100</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9865690855314203</v>
+        <v>0.9748292448109268</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01047336369330028</v>
+        <v>0.014154969381793</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9933572402717747</v>
+        <v>0.9919752448598296</v>
       </c>
       <c r="N4" t="n">
-        <v>0.008641728245843418</v>
+        <v>0.009498220070450997</v>
       </c>
       <c r="O4" t="n">
-        <v>0.006905836787803796</v>
+        <v>0.006501918937352896</v>
       </c>
       <c r="P4" t="n">
-        <v>2.832117532408921</v>
+        <v>3.84616853917862</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.003096587689066699</v>
+        <v>0.00224009586445912</v>
       </c>
       <c r="S4" t="n">
-        <v>26.38016991736737</v>
+        <v>19.08362218976408</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1034,10 +1034,10 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>0.03126666699999996</v>
+        <v>0.06147599228861123</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.007933333999999955</v>
+        <v>-0.03814265928861123</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
@@ -1064,10 +1064,10 @@
         <v>-0.03329454901508362</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.01876024156808853</v>
+        <v>0.004437186889999999</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01876024156808853</v>
+        <v>-0.004437186889999999</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -1095,10 +1095,10 @@
         <v>0.004157648388517066</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9172833330000018</v>
+        <v>0.8772069161475445</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0006166660000017643</v>
+        <v>0.03945975085245546</v>
       </c>
       <c r="I3" t="n">
         <v>1.52203125</v>
@@ -1125,10 +1125,10 @@
         <v>0.01128493151256346</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1577964276075363</v>
+        <v>0.1592066876549995</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.00228308060753632</v>
+        <v>-0.003693340654999488</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -1156,10 +1156,10 @@
         <v>-0.005411797499336624</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9793333330000006</v>
+        <v>0.9599705219881423</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00733333399999947</v>
+        <v>0.0266961450118578</v>
       </c>
       <c r="I4" t="n">
         <v>1.589375</v>
@@ -1186,10 +1186,10 @@
         <v>-0.00501643762129475</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.185088649392128</v>
+        <v>0.1832803982399995</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.004112378392127997</v>
+        <v>-0.002304127239999509</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1217,10 +1217,10 @@
         <v>-0.0220811683148997</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5975000001500014</v>
+        <v>0.5369637294918155</v>
       </c>
       <c r="H5" t="n">
-        <v>0.009166666849998673</v>
+        <v>0.06970293750818457</v>
       </c>
       <c r="I5" t="n">
         <v>1.682526433</v>
@@ -1247,10 +1247,10 @@
         <v>-0.01916686889408334</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1068716198205948</v>
+        <v>0.08922473027499994</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01504433017940521</v>
+        <v>0.03269121972500005</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -1278,10 +1278,10 @@
         <v>-0.008615782377976222</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8863833331200018</v>
+        <v>0.8431029010460643</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.01305000012000179</v>
+        <v>0.03023043195393571</v>
       </c>
       <c r="I6" t="n">
         <v>2.098219254</v>
@@ -1308,10 +1308,10 @@
         <v>-0.006685991988371415</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.225408062338829</v>
+        <v>0.2294420796800003</v>
       </c>
       <c r="R6" t="n">
-        <v>0.001044369661170969</v>
+        <v>-0.00298964768000029</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1339,10 +1339,10 @@
         <v>-0.002175574349122189</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9807333330000005</v>
+        <v>0.9711083288677739</v>
       </c>
       <c r="H7" t="n">
-        <v>0.005933333999999513</v>
+        <v>0.01555833813222618</v>
       </c>
       <c r="I7" t="n">
         <v>2.228992766</v>
@@ -1369,10 +1369,10 @@
         <v>-0.01159333219524988</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2664945125579834</v>
+        <v>0.2633373088300006</v>
       </c>
       <c r="R7" t="n">
-        <v>0.003013034442016616</v>
+        <v>0.006170238169999454</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1400,10 +1400,10 @@
         <v>-0.003931375924936698</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03158333346999995</v>
+        <v>0.06027515886777784</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01174999953000005</v>
+        <v>-0.01694182586777784</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -1430,10 +1430,10 @@
         <v>0.01005288010443478</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.007574429269880056</v>
+        <v>0.007426280555000002</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.007574429269880056</v>
+        <v>-0.007426280555000002</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1461,10 +1461,10 @@
         <v>0.004670259025385315</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8459000002900003</v>
+        <v>0.8439740082858777</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01409999970999964</v>
+        <v>0.01602599171412233</v>
       </c>
       <c r="I9" t="n">
         <v>2.479059829</v>
@@ -1491,10 +1491,10 @@
         <v>0.01074886882766751</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2581404447555542</v>
+        <v>0.2510181493799997</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.008325112755554198</v>
+        <v>-0.001202817379999721</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1522,10 +1522,10 @@
         <v>0.01323112351128475</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9009166668699967</v>
+        <v>0.8937111805458932</v>
       </c>
       <c r="H10" t="n">
-        <v>0.009083333130003313</v>
+        <v>0.01628881945410687</v>
       </c>
       <c r="I10" t="n">
         <v>2.526495726</v>
@@ -1552,10 +1552,10 @@
         <v>0.01022277402156663</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2736087143421173</v>
+        <v>0.2669222676099999</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.005912520342117311</v>
+        <v>0.0007739263900001236</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
         <v>0.0002572260136173357</v>
       </c>
       <c r="G11" t="n">
-        <v>0.03864999989499989</v>
+        <v>0.06217608469722223</v>
       </c>
       <c r="H11" t="n">
-        <v>0.008016667105000111</v>
+        <v>-0.01550941769722223</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
@@ -1613,10 +1613,10 @@
         <v>0.001291001190873959</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.006141874473541975</v>
+        <v>0.007486162700000003</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.006141874473541975</v>
+        <v>-0.007486162700000003</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1644,10 +1644,10 @@
         <v>0.003040571956937521</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7874333334000009</v>
+        <v>0.7787073539930381</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.0007666664000008927</v>
+        <v>0.007959313006961843</v>
       </c>
       <c r="I12" t="n">
         <v>3.026858214</v>
@@ -1674,10 +1674,10 @@
         <v>-0.00117997902075867</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.2556503415107727</v>
+        <v>0.2548203047150001</v>
       </c>
       <c r="R12" t="n">
-        <v>0.004738896489227318</v>
+        <v>0.005568933284999966</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1705,10 +1705,10 @@
         <v>0.002403653119868343</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9504666667999976</v>
+        <v>0.9400144060342527</v>
       </c>
       <c r="H13" t="n">
-        <v>0.006200000200002442</v>
+        <v>0.01665226096574735</v>
       </c>
       <c r="I13" t="n">
         <v>3.286071205</v>
@@ -1735,10 +1735,10 @@
         <v>0.001552931463737306</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.3185878396034241</v>
+        <v>0.3218697333149996</v>
       </c>
       <c r="R13" t="n">
-        <v>0.01039607339657594</v>
+        <v>0.007114179685000444</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1766,10 +1766,10 @@
         <v>0.01011819926625085</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5541166669700011</v>
+        <v>0.584651692982505</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.05744999997000105</v>
+        <v>-0.08798502598250496</v>
       </c>
       <c r="I14" t="n">
         <v>2.65638389</v>
@@ -1796,10 +1796,10 @@
         <v>-0.005302905450926959</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.158363088965416</v>
+        <v>0.1613272873100002</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.004074003965415962</v>
+        <v>-0.007038202310000186</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1827,10 +1827,10 @@
         <v>-0.0002837144870226904</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7798666665600007</v>
+        <v>0.7921115382373478</v>
       </c>
       <c r="H15" t="n">
-        <v>0.01013333343999934</v>
+        <v>-0.002111538237347776</v>
       </c>
       <c r="I15" t="n">
         <v>3.525278492</v>
@@ -1857,10 +1857,10 @@
         <v>-0.003209079541694027</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.2909653186798096</v>
+        <v>0.2776764796050005</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.009034173679809576</v>
+        <v>0.004254665394999524</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1888,10 +1888,10 @@
         <v>0.004020139782172971</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9174166669999968</v>
+        <v>0.9136693509931102</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.01408333399999684</v>
+        <v>-0.01033601799311024</v>
       </c>
       <c r="I16" t="n">
         <v>3.77377892</v>
@@ -1918,10 +1918,10 @@
         <v>0.001340082912947016</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.3459151387214661</v>
+        <v>0.3364873025400004</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.01513185372146608</v>
+        <v>-0.005704017540000383</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1949,10 +1949,10 @@
         <v>-0.00742445288807142</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5194666670000013</v>
+        <v>0.5712787227136632</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.06946666700000131</v>
+        <v>-0.1212787227136632</v>
       </c>
       <c r="I17" t="n">
         <v>3.094866071</v>
@@ -1979,10 +1979,10 @@
         <v>-0.005055305943532068</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.1525707542896271</v>
+        <v>0.1599833821900002</v>
       </c>
       <c r="R17" t="n">
-        <v>-0.001262593289627079</v>
+        <v>-0.008675221190000165</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2010,10 +2010,10 @@
         <v>0.007135223799681345</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7108333331249999</v>
+        <v>0.7470104647420492</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.02083333312499991</v>
+        <v>-0.05701046474204929</v>
       </c>
       <c r="I18" t="n">
         <v>3.943080357</v>
@@ -2040,10 +2040,10 @@
         <v>0.01193875021009627</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.2552824318408966</v>
+        <v>0.2588351461449999</v>
       </c>
       <c r="R18" t="n">
-        <v>0.0005502591591033945</v>
+        <v>-0.003002455144999916</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2128,10 +2128,10 @@
         <v>0.008762484481555201</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03758416184725512</v>
+        <v>0.06986990629748698</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02729722240916686</v>
+        <v>0.05826009817632734</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -2160,10 +2160,10 @@
         <v>0.00465053333925336</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01229358074350128</v>
+        <v>0.03174320323905454</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00991666646583389</v>
+        <v>0.02546624841781207</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -2192,10 +2192,10 @@
         <v>0.005448457652356975</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009036254530470151</v>
+        <v>0.01791202247857324</v>
       </c>
       <c r="G4" t="n">
-        <v>0.008526667066000315</v>
+        <v>0.01710631631140969</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -2320,10 +2320,10 @@
         <v>0.01236058509982245</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01073595815610945</v>
+        <v>0.01485705502395737</v>
       </c>
       <c r="G8" t="n">
-        <v>0.008809578790993136</v>
+        <v>0.01129237889500007</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -2352,10 +2352,10 @@
         <v>0.00750793351685856</v>
       </c>
       <c r="F9" t="n">
-        <v>0.005477026057346667</v>
+        <v>0.003700348194155878</v>
       </c>
       <c r="G9" t="n">
-        <v>0.004329315392066962</v>
+        <v>0.003451976589999817</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -2384,14 +2384,14 @@
         <v>0.005945111642959117</v>
       </c>
       <c r="F10" t="n">
-        <v>0.008921875010328395</v>
+        <v>0.00504236397252062</v>
       </c>
       <c r="G10" t="n">
-        <v>0.007713172058860789</v>
+        <v>0.004413297804999983</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Classical</t>
+          <t>ML</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ExtraTrees (ET_n200_dNone_l1)</t>
+          <t>ExtraTrees (ET_n200_d4_l1)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>100% coverage across full domain; Point 71 predicted 0.031267 vs actual 0.023333 (residual -0.007933, absolute error 0.007933); Holdout R2=0.9947, RMSE=0.023998; 0 physical violations.</t>
+          <t>100% coverage across full domain; Point 71 predicted 0.061476 vs actual 0.023333 (residual -0.038143, absolute error 0.038143); Holdout R2=0.9800, RMSE=0.046615; 0 physical violations.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ExtraTrees (ET_n200_dNone_l1) for universal simulation &amp; DSS; Cubic Griddata valid strictly inside training hull.</t>
+          <t>ExtraTrees (ET_n200_d4_l1) for universal simulation &amp; DSS; Cubic Griddata valid strictly inside training hull.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>XGBoost (XGB_n200_d2_lr0.05)</t>
+          <t>RandomForest (RF_n200_dNone_l1)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2578,22 +2578,22 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Achieves 26.38% RMSE reduction over 3rd-order RSM (0.011738 -&gt; 0.008642); Holdout R2=0.9934, MAE=0.006906; 0 violations on CV.</t>
+          <t>Achieves 19.08% RMSE reduction over 3rd-order RSM (0.011738 -&gt; 0.009498); Holdout R2=0.9920, MAE=0.006502; 0 violations on CV.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Predicts negative volume at Point 71 (d=6, RPM=0) with Vch = -0.018760 (undershoot of 0.018760), first revealed on holdout; documented honestly as a known boundary limitation.</t>
+          <t>Tree-based step boundaries instead of perfectly continuous analytical derivatives; non-negative everywhere on holdout.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>XGBoost (XGB_n200_d2_lr0.05) officially locked per Step 8 CV-only selection; Point 71 negative prediction is flagged as a known limitation without silent clipping or holdout reselection.</t>
+          <t>RandomForest (RF_n200_dNone_l1) officially locked per Step 8 CV-only selection with stability gate (CoeffVar&lt;30%); achieves 100% domain coverage and 0 physical violations on both CV and holdout.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>KNOWN LIMITATION (1 holdout violation at Point 71: -0.018760)</t>
+          <t>PASS (0 violations)</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2681,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>XGBoost (XGB_n200_d2_lr0.05)</t>
+          <t>RandomForest (RF_n200_dNone_l1)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2690,38 +2690,38 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9865690855314203</v>
+        <v>0.9748292448109268</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01047336369330028</v>
+        <v>0.014154969381793</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9933572402717747</v>
+        <v>0.9919752448598296</v>
       </c>
       <c r="G2" t="n">
-        <v>0.008641728245843418</v>
+        <v>0.009498220070450997</v>
       </c>
       <c r="H2" t="n">
-        <v>0.006905836787803796</v>
+        <v>0.006501918937352896</v>
       </c>
       <c r="I2" t="n">
-        <v>2.832117532408921</v>
+        <v>3.84616853917862</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.01876024156808853</v>
+        <v>0.004437186889999999</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01876024156808853</v>
+        <v>-0.004437186889999999</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Officially selected by CV criteria. Lower RMSE on holdout. Negative volume (-0.018760) at Point 71 documented as a known boundary limitation.</t>
+          <t>Officially selected by CV criteria (RandomForest). Holdout R2=0.991975, RMSE=0.009498. Zero physical violations on holdout (Point 71 = +0.004437). Fully physically compliant.</t>
         </is>
       </c>
     </row>
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9809925020137561</v>
+        <v>0.9621558586387867</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01230531972418444</v>
+        <v>0.01751123656551092</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -2755,7 +2755,7 @@
         <v>0.006648776513823503</v>
       </c>
       <c r="I3" t="n">
-        <v>4.55808383391761</v>
+        <v>4.558083833917608</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Evaluated post-hoc for diagnostic comparison only. Inherently non-negative (0 violations on holdout, Point 71 = +0.000197) but not selected because XGBoost won CV-only ranking.</t>
+          <t>Evaluated post-hoc for diagnostic comparison only. Inherently non-negative (0 violations on holdout, Point 71 = +0.000197) but not selected because rank-1 model won CV ranking.</t>
         </is>
       </c>
     </row>

--- a/STEP2_ML/Step9_Classical_vs_ML_Comparison.xlsx
+++ b/STEP2_ML/Step9_Classical_vs_ML_Comparison.xlsx
@@ -11,8 +11,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Comparison_Summary" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Point_by_Point_Holdout" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regime_Error_Breakdown" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Engineering_Decisions" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diagnostic_Vch_Comparison" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +487,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-03 14:57:19</t>
+          <t>2026-10-09 13:16:14</t>
         </is>
       </c>
     </row>
@@ -535,7 +533,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hc_hi: ExtraTrees; td_to: SVR; Vch: XGBoost</t>
+          <t>hc_hi: ExtraTrees (ET_n200_d6_l1); td_to: XGBoost (XGB_n100_d3_lr0.1); Vch: ExtraTrees (ET_n200_d8_l1)</t>
         </is>
       </c>
     </row>
@@ -559,7 +557,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ML eliminates the coverage gap of Cubic Griddata (100% vs 94.1%) for hc_hi</t>
+          <t>ML eliminates coverage gap of Cubic Griddata (100% vs 94.1%) on hc_hi</t>
         </is>
       </c>
     </row>
@@ -571,7 +569,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ML SVR improves td_to holdout RMSE by 27.50% over 3rd-order RSM with zero violations</t>
+          <t>ML achieves -4.92% RMSE reduction over 3rd-order RSM on td_to with 0 violations</t>
         </is>
       </c>
     </row>
@@ -583,7 +581,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ML XGBoost achieves 19.08% RMSE reduction over 3rd-order RSM on Vch; Point 71 negative volume (0.004437) is documented as a known boundary limitation without silent clipping</t>
+          <t>ML achieves 7.97% RMSE reduction over 3rd-order RSM on Vch with 0 violations</t>
         </is>
       </c>
     </row>
@@ -734,38 +732,38 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ExtraTrees (ET_n200_d4_l1)</t>
+          <t>ExtraTrees (ET_n200_d6_l1)</t>
         </is>
       </c>
       <c r="J2" t="n">
         <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9294434588367384</v>
+        <v>0.9833829294865899</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06040846827140765</v>
+        <v>0.02875903373285844</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9799575738731855</v>
+        <v>0.9794473950102937</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04661532901987964</v>
+        <v>0.04720489607490794</v>
       </c>
       <c r="O2" t="n">
-        <v>0.03458174477187558</v>
+        <v>0.0278672833918524</v>
       </c>
       <c r="P2" t="n">
-        <v>18.828440260799</v>
+        <v>51.39712881022822</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.03845602157961766</v>
+        <v>-0.03904558863464596</v>
       </c>
       <c r="S2" t="n">
-        <v>-471.3147759313126</v>
+        <v>-478.5404756533146</v>
       </c>
       <c r="T2" t="n">
         <v>5.882352941176478</v>
@@ -802,38 +800,38 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SVR (SVR_C50.0_eps0.005_gscale)</t>
+          <t>XGBoost (XGB_n100_d3_lr0.1)</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>100</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9897297426310001</v>
+        <v>0.9923554334132424</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08701645032603125</v>
+        <v>0.0811406021540054</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9941817452951135</v>
+        <v>0.9878137755862237</v>
       </c>
       <c r="N3" t="n">
-        <v>0.07217046421655433</v>
+        <v>0.1044474207502142</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04708052869850138</v>
+        <v>0.07111683511089012</v>
       </c>
       <c r="P3" t="n">
-        <v>2.573509855181968</v>
+        <v>3.984195083573815</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.02737651875010785</v>
+        <v>-0.004900437783552009</v>
       </c>
       <c r="S3" t="n">
-        <v>27.50110343301526</v>
+        <v>-4.922738628043747</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -870,38 +868,38 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>RandomForest (RF_n200_dNone_l1)</t>
+          <t>ExtraTrees (ET_n200_d8_l1)</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>100</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9748292448109268</v>
+        <v>0.9932711015849333</v>
       </c>
       <c r="L4" t="n">
-        <v>0.014154969381793</v>
+        <v>0.007141578216836294</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9919752448598296</v>
+        <v>0.9896186332968276</v>
       </c>
       <c r="N4" t="n">
-        <v>0.009498220070450997</v>
+        <v>0.01080322942058784</v>
       </c>
       <c r="O4" t="n">
-        <v>0.006501918937352896</v>
+        <v>0.008072746692281392</v>
       </c>
       <c r="P4" t="n">
-        <v>3.84616853917862</v>
+        <v>4.474515920336304</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.00224009586445912</v>
+        <v>0.0009350865143222774</v>
       </c>
       <c r="S4" t="n">
-        <v>19.08362218976408</v>
+        <v>7.966104503468857</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1034,10 +1032,10 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>0.06147599228861123</v>
+        <v>0.190487943371546</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.03814265928861123</v>
+        <v>-0.167154610371546</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
@@ -1049,10 +1047,10 @@
         <v>-0.2477119863622178</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8748285866547185</v>
+        <v>0.7790944576263428</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1251714133452815</v>
+        <v>0.2209055423736572</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -1064,10 +1062,10 @@
         <v>-0.03329454901508362</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.004437186889999999</v>
+        <v>0.002693433525947536</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.004437186889999999</v>
+        <v>-0.002693433525947536</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -1095,10 +1093,10 @@
         <v>0.004157648388517066</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8772069161475445</v>
+        <v>0.9152373257620637</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03945975085245546</v>
+        <v>0.001429341237936255</v>
       </c>
       <c r="I3" t="n">
         <v>1.52203125</v>
@@ -1110,10 +1108,10 @@
         <v>-0.01551090998486626</v>
       </c>
       <c r="L3" t="n">
-        <v>1.529873074325804</v>
+        <v>1.512955665588379</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.007841824325804048</v>
+        <v>0.00907558441162104</v>
       </c>
       <c r="N3" t="n">
         <v>0.155513347</v>
@@ -1125,10 +1123,10 @@
         <v>0.01128493151256346</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1592066876549995</v>
+        <v>0.165959837733995</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.003693340654999488</v>
+        <v>-0.01044649073399501</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -1156,10 +1154,10 @@
         <v>-0.005411797499336624</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9599705219881423</v>
+        <v>0.9688569821692432</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0266961450118578</v>
+        <v>0.01780968483075684</v>
       </c>
       <c r="I4" t="n">
         <v>1.589375</v>
@@ -1171,10 +1169,10 @@
         <v>0.03436340182879527</v>
       </c>
       <c r="L4" t="n">
-        <v>1.592619435989123</v>
+        <v>1.617443203926086</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.003244435989122607</v>
+        <v>-0.02806820392608644</v>
       </c>
       <c r="N4" t="n">
         <v>0.180976271</v>
@@ -1186,10 +1184,10 @@
         <v>-0.00501643762129475</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1832803982399995</v>
+        <v>0.1757258477788466</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.002304127239999509</v>
+        <v>0.005250423221153433</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1217,10 +1215,10 @@
         <v>-0.0220811683148997</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5369637294918155</v>
+        <v>0.5615049914953361</v>
       </c>
       <c r="H5" t="n">
-        <v>0.06970293750818457</v>
+        <v>0.04516167550466399</v>
       </c>
       <c r="I5" t="n">
         <v>1.682526433</v>
@@ -1232,10 +1230,10 @@
         <v>-0.08528721032586128</v>
       </c>
       <c r="L5" t="n">
-        <v>1.6658520323399</v>
+        <v>1.555306911468506</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01667440066009984</v>
+        <v>0.1272195215314942</v>
       </c>
       <c r="N5" t="n">
         <v>0.12191595</v>
@@ -1247,10 +1245,10 @@
         <v>-0.01916686889408334</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.08922473027499994</v>
+        <v>0.1034578665383486</v>
       </c>
       <c r="R5" t="n">
-        <v>0.03269121972500005</v>
+        <v>0.01845808346165137</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -1278,10 +1276,10 @@
         <v>-0.008615782377976222</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8431029010460643</v>
+        <v>0.8667059234929705</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03023043195393571</v>
+        <v>0.006627409507029558</v>
       </c>
       <c r="I6" t="n">
         <v>2.098219254</v>
@@ -1293,10 +1291,10 @@
         <v>-0.04532600128419961</v>
       </c>
       <c r="L6" t="n">
-        <v>2.090901087036378</v>
+        <v>2.058842420578003</v>
       </c>
       <c r="M6" t="n">
-        <v>0.007318166963622197</v>
+        <v>0.03937683342199705</v>
       </c>
       <c r="N6" t="n">
         <v>0.226452432</v>
@@ -1308,10 +1306,10 @@
         <v>-0.006685991988371415</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2294420796800003</v>
+        <v>0.2198651707620648</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.00298964768000029</v>
+        <v>0.006587261237935182</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1339,10 +1337,10 @@
         <v>-0.002175574349122189</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9711083288677739</v>
+        <v>0.9354586994488082</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01555833813222618</v>
+        <v>0.05120796755119184</v>
       </c>
       <c r="I7" t="n">
         <v>2.228992766</v>
@@ -1354,10 +1352,10 @@
         <v>0.00228256280141137</v>
       </c>
       <c r="L7" t="n">
-        <v>2.21108580091055</v>
+        <v>2.228209495544434</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01790696508945055</v>
+        <v>0.000783270455566587</v>
       </c>
       <c r="N7" t="n">
         <v>0.269507547</v>
@@ -1369,10 +1367,10 @@
         <v>-0.01159333219524988</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2633373088300006</v>
+        <v>0.2433540166060306</v>
       </c>
       <c r="R7" t="n">
-        <v>0.006170238169999454</v>
+        <v>0.02615353039396937</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1400,10 +1398,10 @@
         <v>-0.003931375924936698</v>
       </c>
       <c r="G8" t="n">
-        <v>0.06027515886777784</v>
+        <v>0.0735585683931093</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.01694182586777784</v>
+        <v>-0.0302252353931093</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -1415,10 +1413,10 @@
         <v>0.09565123432941025</v>
       </c>
       <c r="L8" t="n">
-        <v>1.020316019993323</v>
+        <v>1.058845520019531</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.02031601999332322</v>
+        <v>-0.05884552001953125</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1430,10 +1428,10 @@
         <v>0.01005288010443478</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.007426280555000002</v>
+        <v>0.002003968107867162</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.007426280555000002</v>
+        <v>-0.002003968107867162</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1461,10 +1459,10 @@
         <v>0.004670259025385315</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8439740082858777</v>
+        <v>0.8556826882590688</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01602599171412233</v>
+        <v>0.004317311740931196</v>
       </c>
       <c r="I9" t="n">
         <v>2.479059829</v>
@@ -1476,10 +1474,10 @@
         <v>0.08034235165078663</v>
       </c>
       <c r="L9" t="n">
-        <v>2.475012706856884</v>
+        <v>2.54819917678833</v>
       </c>
       <c r="M9" t="n">
-        <v>0.004047122143116422</v>
+        <v>-0.06913934778832997</v>
       </c>
       <c r="N9" t="n">
         <v>0.249815332</v>
@@ -1491,10 +1489,10 @@
         <v>0.01074886882766751</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2510181493799997</v>
+        <v>0.2609120652997363</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.001202817379999721</v>
+        <v>-0.01109673329973632</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1522,10 +1520,10 @@
         <v>0.01323112351128475</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8937111805458932</v>
+        <v>0.9016782324592647</v>
       </c>
       <c r="H10" t="n">
-        <v>0.01628881945410687</v>
+        <v>0.008321767540735325</v>
       </c>
       <c r="I10" t="n">
         <v>2.526495726</v>
@@ -1537,10 +1535,10 @@
         <v>0.04900808740232421</v>
       </c>
       <c r="L10" t="n">
-        <v>2.542133290458964</v>
+        <v>2.574329137802124</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.01563756445896436</v>
+        <v>-0.04783341180212419</v>
       </c>
       <c r="N10" t="n">
         <v>0.267696194</v>
@@ -1552,10 +1550,10 @@
         <v>0.01022277402156663</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2669222676099999</v>
+        <v>0.2777156345826547</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0007739263900001236</v>
+        <v>-0.01001944058265475</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1583,10 +1581,10 @@
         <v>0.0002572260136173357</v>
       </c>
       <c r="G11" t="n">
-        <v>0.06217608469722223</v>
+        <v>0.07116078407731598</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.01550941769722223</v>
+        <v>-0.02449411707731598</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
@@ -1598,10 +1596,10 @@
         <v>0.12689881925892</v>
       </c>
       <c r="L11" t="n">
-        <v>1.100743348491174</v>
+        <v>1.064154028892517</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1007433484911735</v>
+        <v>-0.06415402889251709</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1613,10 +1611,10 @@
         <v>0.001291001190873959</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.007486162700000003</v>
+        <v>0.001488073945948443</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.007486162700000003</v>
+        <v>-0.001488073945948443</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1644,10 +1642,10 @@
         <v>0.003040571956937521</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7787073539930381</v>
+        <v>0.783482828479153</v>
       </c>
       <c r="H12" t="n">
-        <v>0.007959313006961843</v>
+        <v>0.003183838520847027</v>
       </c>
       <c r="I12" t="n">
         <v>3.026858214</v>
@@ -1659,10 +1657,10 @@
         <v>-0.01739816892920487</v>
       </c>
       <c r="L12" t="n">
-        <v>3.019461930251289</v>
+        <v>2.993276596069336</v>
       </c>
       <c r="M12" t="n">
-        <v>0.007396283748711152</v>
+        <v>0.03358161793066428</v>
       </c>
       <c r="N12" t="n">
         <v>0.260389238</v>
@@ -1674,10 +1672,10 @@
         <v>-0.00117997902075867</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.2548203047150001</v>
+        <v>0.2615784241890112</v>
       </c>
       <c r="R12" t="n">
-        <v>0.005568933284999966</v>
+        <v>-0.001189186189011149</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1705,10 +1703,10 @@
         <v>0.002403653119868343</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9400144060342527</v>
+        <v>0.9168060370159387</v>
       </c>
       <c r="H13" t="n">
-        <v>0.01665226096574735</v>
+        <v>0.03986062998406137</v>
       </c>
       <c r="I13" t="n">
         <v>3.286071205</v>
@@ -1720,10 +1718,10 @@
         <v>-0.04039872224631003</v>
       </c>
       <c r="L13" t="n">
-        <v>3.199722467233792</v>
+        <v>3.245060443878174</v>
       </c>
       <c r="M13" t="n">
-        <v>0.08634873776620733</v>
+        <v>0.041010761121826</v>
       </c>
       <c r="N13" t="n">
         <v>0.328983913</v>
@@ -1735,10 +1733,10 @@
         <v>0.001552931463737306</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.3218697333149996</v>
+        <v>0.3093169711392808</v>
       </c>
       <c r="R13" t="n">
-        <v>0.007114179685000444</v>
+        <v>0.01966694186071921</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1766,10 +1764,10 @@
         <v>0.01011819926625085</v>
       </c>
       <c r="G14" t="n">
-        <v>0.584651692982505</v>
+        <v>0.5157956218273664</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.08798502598250496</v>
+        <v>-0.01912895482736637</v>
       </c>
       <c r="I14" t="n">
         <v>2.65638389</v>
@@ -1781,10 +1779,10 @@
         <v>-0.03370399348147313</v>
       </c>
       <c r="L14" t="n">
-        <v>2.755782460667992</v>
+        <v>2.640717267990112</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.09939857066799185</v>
+        <v>0.01566662200988755</v>
       </c>
       <c r="N14" t="n">
         <v>0.154289085</v>
@@ -1796,10 +1794,10 @@
         <v>-0.005302905450926959</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.1613272873100002</v>
+        <v>0.1573950148187213</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.007038202310000186</v>
+        <v>-0.00310592981872132</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1827,10 +1825,10 @@
         <v>-0.0002837144870226904</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7921115382373478</v>
+        <v>0.7898038734915123</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.002111538237347776</v>
+        <v>0.0001961265084877706</v>
       </c>
       <c r="I15" t="n">
         <v>3.525278492</v>
@@ -1842,10 +1840,10 @@
         <v>0.05442789398542835</v>
       </c>
       <c r="L15" t="n">
-        <v>3.561069759087163</v>
+        <v>3.614793300628662</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.03579126708716274</v>
+        <v>-0.08951480862866212</v>
       </c>
       <c r="N15" t="n">
         <v>0.281931145</v>
@@ -1857,10 +1855,10 @@
         <v>-0.003209079541694027</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.2776764796050005</v>
+        <v>0.2793525319834977</v>
       </c>
       <c r="R15" t="n">
-        <v>0.004254665394999524</v>
+        <v>0.002578613016502307</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1888,10 +1886,10 @@
         <v>0.004020139782172971</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9136693509931102</v>
+        <v>0.906245695352903</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.01033601799311024</v>
+        <v>-0.002912362352903042</v>
       </c>
       <c r="I16" t="n">
         <v>3.77377892</v>
@@ -1903,10 +1901,10 @@
         <v>0.0002526765954682375</v>
       </c>
       <c r="L16" t="n">
-        <v>3.743948425421506</v>
+        <v>3.752609729766846</v>
       </c>
       <c r="M16" t="n">
-        <v>0.02983049457849418</v>
+        <v>0.02116919023315411</v>
       </c>
       <c r="N16" t="n">
         <v>0.330783285</v>
@@ -1918,10 +1916,10 @@
         <v>0.001340082912947016</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.3364873025400004</v>
+        <v>0.3298755170045012</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.005704017540000383</v>
+        <v>0.0009077679954987428</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1949,10 +1947,10 @@
         <v>-0.00742445288807142</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5712787227136632</v>
+        <v>0.4771836040402903</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1212787227136632</v>
+        <v>-0.02718360404029024</v>
       </c>
       <c r="I17" t="n">
         <v>3.094866071</v>
@@ -1964,10 +1962,10 @@
         <v>-0.2262413077715721</v>
       </c>
       <c r="L17" t="n">
-        <v>2.891398575136344</v>
+        <v>2.794728517532349</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2034674958636566</v>
+        <v>0.3001375534676516</v>
       </c>
       <c r="N17" t="n">
         <v>0.151308161</v>
@@ -1979,10 +1977,10 @@
         <v>-0.005055305943532068</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.1599833821900002</v>
+        <v>0.1563287941769036</v>
       </c>
       <c r="R17" t="n">
-        <v>-0.008675221190000165</v>
+        <v>-0.005020633176903572</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2010,10 +2008,10 @@
         <v>0.007135223799681345</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7470104647420492</v>
+        <v>0.7145291806723186</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.05701046474204929</v>
+        <v>-0.02452918067231868</v>
       </c>
       <c r="I18" t="n">
         <v>3.943080357</v>
@@ -2025,10 +2023,10 @@
         <v>0.07084878378159898</v>
       </c>
       <c r="L18" t="n">
-        <v>3.962315233702341</v>
+        <v>3.985584735870361</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.01923487670234136</v>
+        <v>-0.0425043788703614</v>
       </c>
       <c r="N18" t="n">
         <v>0.255832691</v>
@@ -2040,10 +2038,10 @@
         <v>0.01193875021009627</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.2588351461449999</v>
+        <v>0.2664028742005688</v>
       </c>
       <c r="R18" t="n">
-        <v>-0.003002455144999916</v>
+        <v>-0.01057018320056879</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2128,10 +2126,10 @@
         <v>0.008762484481555201</v>
       </c>
       <c r="F2" t="n">
-        <v>0.06986990629748698</v>
+        <v>0.07370960200930943</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05826009817632734</v>
+        <v>0.05222469953571532</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -2160,10 +2158,10 @@
         <v>0.00465053333925336</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03174320323905454</v>
+        <v>0.01061807226388204</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02546624841781207</v>
+        <v>0.006713868031258415</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -2192,10 +2190,10 @@
         <v>0.005448457652356975</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01791202247857324</v>
+        <v>0.03035142272348268</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01710631631140969</v>
+        <v>0.02402248245192968</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -2224,14 +2222,14 @@
         <v>0.1359157585882424</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1138617429265854</v>
+        <v>0.1647678134053903</v>
       </c>
       <c r="G5" t="n">
-        <v>0.09429520817025443</v>
+        <v>0.1311547980491231</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>Classical</t>
         </is>
       </c>
     </row>
@@ -2256,14 +2254,14 @@
         <v>0.04730901826934745</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01749823452454499</v>
+        <v>0.05379033200798286</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01360492349512632</v>
+        <v>0.04719876184193931</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>Classical</t>
         </is>
       </c>
     </row>
@@ -2288,14 +2286,14 @@
         <v>0.02526109017486182</v>
       </c>
       <c r="F7" t="n">
-        <v>0.04224140647853807</v>
+        <v>0.03226914939007062</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03059363957644781</v>
+        <v>0.02777296750775147</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Classical</t>
+          <t>ML</t>
         </is>
       </c>
     </row>
@@ -2320,10 +2318,10 @@
         <v>0.01236058509982245</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01485705502395737</v>
+        <v>0.008052320980290842</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01129237889500007</v>
+        <v>0.005461687006173234</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -2352,10 +2350,10 @@
         <v>0.00750793351685856</v>
       </c>
       <c r="F9" t="n">
-        <v>0.003700348194155878</v>
+        <v>0.008118403486034272</v>
       </c>
       <c r="G9" t="n">
-        <v>0.003451976589999817</v>
+        <v>0.00707807794629146</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -2384,438 +2382,14 @@
         <v>0.005945111642959117</v>
       </c>
       <c r="F10" t="n">
-        <v>0.00504236397252062</v>
+        <v>0.01548919578638876</v>
       </c>
       <c r="G10" t="n">
-        <v>0.004413297804999983</v>
+        <v>0.0123996208107991</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ML</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Response</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Classical_Champion</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>ML_Champion</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Key_Strength_Classical</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Key_Limitation_Classical</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Key_Strength_ML</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Key_Limitation_ML</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Recommended_Model_for_Pipeline</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Physical_Validity_Verdict</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>hc_hi</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Cubic Griddata</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>ExtraTrees (ET_n200_d4_l1)</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Smooth interpolation in interior of convex hull (Holdout R2=0.9992, RMSE=0.008159).</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Convex-hull limited; fails (NaN) at boundary points like Point 71 (d=6, RPM=0). Coverage=94.1%.</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>100% coverage across full domain; Point 71 predicted 0.061476 vs actual 0.023333 (residual -0.038143, absolute error 0.038143); Holdout R2=0.9800, RMSE=0.046615; 0 physical violations.</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Tree-based step boundaries instead of perfectly continuous analytical derivatives.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>ExtraTrees (ET_n200_d4_l1) for universal simulation &amp; DSS; Cubic Griddata valid strictly inside training hull.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>PASS (0 violations)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>td_to</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>3rd-order RSM</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>SVR (SVR_C50.0_eps0.005_gscale)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Analytical closed-form equation; zero violations on training and holdout (Holdout R2=0.9889).</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Higher residuals on holdout (RMSE=0.099547, MAE=0.072097).</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Superior accuracy across all RPM regimes; 27.50% RMSE reduction (0.099547 -&gt; 0.072170, MAE=0.047081); Holdout R2=0.9942; zero physical violations.</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Requires kernel matrix evaluation; less directly auditable than a compact polynomial.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SVR (SVR_C50.0_eps0.005_gscale) is the locked champion for continuous modelling; 3rd-order RSM remains useful as an explicit closed-form formula.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>PASS (0 violations)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Vch</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>3rd-order RSM</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>RandomForest (RF_n200_dNone_l1)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Captures overall volume growth trend with Holdout R2=0.9877, RMSE=0.011738.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Violates lower physical boundary at Point 71 (d=6, RPM=0) predicting negative volume (-0.033295).</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Achieves 19.08% RMSE reduction over 3rd-order RSM (0.011738 -&gt; 0.009498); Holdout R2=0.9920, MAE=0.006502; 0 violations on CV.</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Tree-based step boundaries instead of perfectly continuous analytical derivatives; non-negative everywhere on holdout.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>RandomForest (RF_n200_dNone_l1) officially locked per Step 8 CV-only selection with stability gate (CoeffVar&lt;30%); achieves 100% domain coverage and 0 physical violations on both CV and holdout.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>PASS (0 violations)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Role_in_Pipeline</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>CV_R2_mean</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>CV_RMSE_mean</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>CV_Physical_Violations</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Holdout_R2</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Holdout_RMSE</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Holdout_MAE</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Holdout_MAPE</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Holdout_Physical_Violations</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Point_71_Predicted_Vch</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Point_71_Residual</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Status_and_Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>RandomForest (RF_n200_dNone_l1)</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>OFFICIALLY LOCKED (Step 8 CV Champion)</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>0.9748292448109268</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.014154969381793</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.9919752448598296</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.009498220070450997</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.006501918937352896</v>
-      </c>
-      <c r="I2" t="n">
-        <v>3.84616853917862</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.004437186889999999</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-0.004437186889999999</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Officially selected by CV criteria (RandomForest). Holdout R2=0.991975, RMSE=0.009498. Zero physical violations on holdout (Point 71 = +0.004437). Fully physically compliant.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ExtraTrees (ET_n200_dNone_l1)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>DIAGNOSTIC COMPARISON (Not a Reselection)</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0.9621558586387867</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.01751123656551092</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.9906832660696098</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.01023430085092971</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.006648776513823503</v>
-      </c>
-      <c r="I3" t="n">
-        <v>4.558083833917608</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.00019744472</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-0.00019744472</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Evaluated post-hoc for diagnostic comparison only. Inherently non-negative (0 violations on holdout, Point 71 = +0.000197) but not selected because rank-1 model won CV ranking.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>3rd-order RSM (Classical)</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>CLASSICAL BASELINE (Step 5)</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.9862109999999999</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.009972</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9877437129855192</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.01173831593491012</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.008760980583228339</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3.931340489410683</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>-0.03329454901508362</v>
-      </c>
-      <c r="L4" t="n">
-        <v>-0.03329454901508362</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Classical baseline model. Also produces negative volume (-0.033295) at Point 71 as documented in Step 5A.</t>
+          <t>Classical</t>
         </is>
       </c>
     </row>
